--- a/data/trans_orig/P57_AC_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57_AC_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2007</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2007 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>496378</t>
+          <t>496080</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>540950</t>
+          <t>542960</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>501458</t>
+          <t>498458</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>544204</t>
+          <t>544608</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,85%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1009402</t>
+          <t>1009906</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1072555</t>
+          <t>1072069</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>77,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>153062</t>
+          <t>151052</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>197634</t>
+          <t>197932</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>144147</t>
+          <t>143743</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>186893</t>
+          <t>189893</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>309808</t>
+          <t>310294</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>372961</t>
+          <t>372457</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,94%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>617804</t>
+          <t>618806</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>678536</t>
+          <t>675483</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>670877</t>
+          <t>675240</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>729637</t>
+          <t>729738</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,45%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1312626</t>
+          <t>1310389</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1390552</t>
+          <t>1392877</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,25%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>282180</t>
+          <t>285233</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>342912</t>
+          <t>341910</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,69%</t>
+          <t>35,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>237605</t>
+          <t>237504</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>296365</t>
+          <t>292002</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>537406</t>
+          <t>535081</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>615332</t>
+          <t>617569</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>392699</t>
+          <t>393899</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>444977</t>
+          <t>446121</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>422353</t>
+          <t>423148</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>469907</t>
+          <t>468938</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>832271</t>
+          <t>829903</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>903381</t>
+          <t>898209</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,09%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>65,93%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>233532</t>
+          <t>232388</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>285810</t>
+          <t>284610</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>213934</t>
+          <t>214903</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>261488</t>
+          <t>260693</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>458969</t>
+          <t>464141</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>530079</t>
+          <t>532447</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,08%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>609549</t>
+          <t>608594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>665668</t>
+          <t>663045</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>687155</t>
+          <t>685603</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>745708</t>
+          <t>744023</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1315739</t>
+          <t>1316175</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1395058</t>
+          <t>1395635</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>66,51%</t>
+          <t>66,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275004</t>
+          <t>277627</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>331123</t>
+          <t>332078</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>291924</t>
+          <t>293609</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>350477</t>
+          <t>352029</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>583246</t>
+          <t>582669</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>662565</t>
+          <t>662129</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,47%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2170969</t>
+          <t>2172811</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2275537</t>
+          <t>2281084</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,51%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2333250</t>
+          <t>2334164</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2435811</t>
+          <t>2444053</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,09%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4539778</t>
+          <t>4540249</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4688116</t>
+          <t>4681898</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,49%</t>
+          <t>70,39%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>998372</t>
+          <t>992825</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1102940</t>
+          <t>1101098</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>941255</t>
+          <t>933013</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1043816</t>
+          <t>1042902</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1962859</t>
+          <t>1969077</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2111197</t>
+          <t>2110726</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,51%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2012</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2012 (tasa de respuesta: 99,31%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>405207</t>
+          <t>402676</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>455635</t>
+          <t>455051</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,07%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>463144</t>
+          <t>461011</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>512410</t>
+          <t>513410</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>879945</t>
+          <t>882372</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>954139</t>
+          <t>955408</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,64%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>242177</t>
+          <t>242761</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292605</t>
+          <t>295136</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>181790</t>
+          <t>180790</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>231056</t>
+          <t>233189</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>437873</t>
+          <t>436604</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>512067</t>
+          <t>509640</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,79%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>631720</t>
+          <t>635185</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>692145</t>
+          <t>694423</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>720832</t>
+          <t>720513</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>781264</t>
+          <t>778645</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1372000</t>
+          <t>1373223</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1458049</t>
+          <t>1457010</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,6%</t>
+          <t>71,55%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>316161</t>
+          <t>313883</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>376586</t>
+          <t>373121</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>246842</t>
+          <t>249461</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>307274</t>
+          <t>307593</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>578363</t>
+          <t>579402</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>664412</t>
+          <t>663189</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,57%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>448231</t>
+          <t>444974</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>504298</t>
+          <t>506777</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,74%</t>
+          <t>59,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>501028</t>
+          <t>501287</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>554515</t>
+          <t>554384</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>965637</t>
+          <t>964089</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1043681</t>
+          <t>1043129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,36%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,44%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>246021</t>
+          <t>243542</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>302088</t>
+          <t>305345</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,26%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>219253</t>
+          <t>219384</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>272740</t>
+          <t>272481</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>480406</t>
+          <t>480958</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>558450</t>
+          <t>559998</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>652199</t>
+          <t>654745</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>709492</t>
+          <t>711408</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>795082</t>
+          <t>794413</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>848113</t>
+          <t>848920</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1465327</t>
+          <t>1469872</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1542739</t>
+          <t>1546402</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,92%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>233068</t>
+          <t>231152</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>290361</t>
+          <t>287815</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>194045</t>
+          <t>193238</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>247076</t>
+          <t>247745</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>441979</t>
+          <t>438316</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>519391</t>
+          <t>514846</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2195742</t>
+          <t>2198487</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2312300</t>
+          <t>2310203</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,6%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2536064</t>
+          <t>2540611</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2640140</t>
+          <t>2644727</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4767294</t>
+          <t>4763531</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4924822</t>
+          <t>4918237</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1086697</t>
+          <t>1088794</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1203255</t>
+          <t>1200510</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,4%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>898092</t>
+          <t>893505</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1002168</t>
+          <t>997621</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2012407</t>
+          <t>2018992</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2169935</t>
+          <t>2173698</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2016</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2016 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>502851</t>
+          <t>503819</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>546309</t>
+          <t>547481</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,76%</t>
+          <t>74,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>538068</t>
+          <t>534675</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>576154</t>
+          <t>575447</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1054010</t>
+          <t>1056548</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1111023</t>
+          <t>1111498</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,79%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>126345</t>
+          <t>125173</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>169803</t>
+          <t>168835</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93800</t>
+          <t>94507</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>131886</t>
+          <t>135279</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>231585</t>
+          <t>231110</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>288598</t>
+          <t>286060</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,31%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>752342</t>
+          <t>751709</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>806088</t>
+          <t>808771</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,16%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>839871</t>
+          <t>839626</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>886873</t>
+          <t>890284</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1606670</t>
+          <t>1606270</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1681533</t>
+          <t>1683892</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,81%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>212266</t>
+          <t>209583</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>266012</t>
+          <t>266645</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>153079</t>
+          <t>149668</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>200081</t>
+          <t>200326</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>376774</t>
+          <t>374415</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>451637</t>
+          <t>452037</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,96%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>604903</t>
+          <t>606641</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>649349</t>
+          <t>647912</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>626173</t>
+          <t>628404</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>669987</t>
+          <t>670433</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1243908</t>
+          <t>1245641</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1307597</t>
+          <t>1305886</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,49%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102345</t>
+          <t>103782</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>146791</t>
+          <t>145053</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>105768</t>
+          <t>105322</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>149582</t>
+          <t>147351</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>219851</t>
+          <t>221562</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>283540</t>
+          <t>281807</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>707005</t>
+          <t>711487</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>758235</t>
+          <t>760404</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>789930</t>
+          <t>791719</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>844935</t>
+          <t>843961</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1517641</t>
+          <t>1516486</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1587517</t>
+          <t>1589244</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,66%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>176011</t>
+          <t>173842</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>227241</t>
+          <t>222759</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>191085</t>
+          <t>192059</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>246090</t>
+          <t>244301</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>382748</t>
+          <t>381021</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>452624</t>
+          <t>453779</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,03%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2618813</t>
+          <t>2620694</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2715505</t>
+          <t>2717371</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2847958</t>
+          <t>2844493</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2934358</t>
+          <t>2937690</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5495187</t>
+          <t>5497943</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5628988</t>
+          <t>5625830</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,66%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,55%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>661443</t>
+          <t>659577</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>758135</t>
+          <t>756254</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>587322</t>
+          <t>583990</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>673722</t>
+          <t>677187</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1269641</t>
+          <t>1272799</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1403442</t>
+          <t>1400686</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,3%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con apoyo confidencial bajo (Duke) en 2023</t>
+          <t>Población con apoyo confidencial bajo (Duke) en 2023 (tasa de respuesta: 98,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>337033</t>
+          <t>334289</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>393204</t>
+          <t>393082</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>386845</t>
+          <t>386820</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>429645</t>
+          <t>431261</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>738470</t>
+          <t>735417</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>808162</t>
+          <t>807426</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,56%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>236671</t>
+          <t>236793</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>292842</t>
+          <t>295586</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>231024</t>
+          <t>229408</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>273824</t>
+          <t>273849</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>482383</t>
+          <t>483119</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>552075</t>
+          <t>555128</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,44%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>43,01%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>331826</t>
+          <t>309035</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>770058</t>
+          <t>766186</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,05%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>602083</t>
+          <t>600150</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>652587</t>
+          <t>651886</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>63,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>833059</t>
+          <t>816545</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1398601</t>
+          <t>1397766</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,58%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>413777</t>
+          <t>417649</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>852009</t>
+          <t>874800</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>295039</t>
+          <t>295740</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>345543</t>
+          <t>347476</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>732861</t>
+          <t>733696</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1298403</t>
+          <t>1314917</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>61,69%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>416982</t>
+          <t>416787</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>478486</t>
+          <t>477995</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>372887</t>
+          <t>375365</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>472125</t>
+          <t>472534</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>51,68%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>815294</t>
+          <t>805862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>933093</t>
+          <t>932733</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,7%</t>
+          <t>65,68%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>220174</t>
+          <t>220665</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>281678</t>
+          <t>281873</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>249368</t>
+          <t>248959</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>348606</t>
+          <t>346128</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>487059</t>
+          <t>487419</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>604858</t>
+          <t>614290</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>34,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,59%</t>
+          <t>43,26%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>501323</t>
+          <t>500287</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>568819</t>
+          <t>568636</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>464514</t>
+          <t>485438</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>653544</t>
+          <t>656680</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>45,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>985381</t>
+          <t>1010207</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1198279</t>
+          <t>1199175</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>60,13%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347242</t>
+          <t>347425</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>414738</t>
+          <t>415774</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>424544</t>
+          <t>421408</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>613574</t>
+          <t>592650</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>795870</t>
+          <t>794974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1008768</t>
+          <t>983942</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>49,34%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1473323</t>
+          <t>1502962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2122379</t>
+          <t>2115993</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1927645</t>
+          <t>1933782</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2155887</t>
+          <t>2152435</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3468951</t>
+          <t>3540564</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4218069</t>
+          <t>4221190</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,74%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>61,75%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1306052</t>
+          <t>1312438</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1955108</t>
+          <t>1925469</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1251989</t>
+          <t>1255441</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1480231</t>
+          <t>1474094</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,44%</t>
+          <t>43,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2618238</t>
+          <t>2615117</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3367356</t>
+          <t>3295743</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57_AC_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P57_AC_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>496080</t>
+          <t>496467</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>542960</t>
+          <t>541088</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>77,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>498458</t>
+          <t>497478</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>544608</t>
+          <t>544693</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1009906</t>
+          <t>1012738</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1072069</t>
+          <t>1074185</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>151052</t>
+          <t>152924</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>197932</t>
+          <t>197545</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>143743</t>
+          <t>143658</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>189893</t>
+          <t>190873</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>310294</t>
+          <t>308178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>372457</t>
+          <t>369625</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>618806</t>
+          <t>621550</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>675483</t>
+          <t>678478</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>675240</t>
+          <t>675417</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>729738</t>
+          <t>729311</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1310389</t>
+          <t>1309482</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1392877</t>
+          <t>1393894</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>72,3%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>285233</t>
+          <t>282238</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>341910</t>
+          <t>339166</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>237504</t>
+          <t>237931</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>292002</t>
+          <t>291825</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>535081</t>
+          <t>534064</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>617569</t>
+          <t>618476</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>393899</t>
+          <t>394282</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>446121</t>
+          <t>444750</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>423148</t>
+          <t>421110</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>468938</t>
+          <t>469488</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>829903</t>
+          <t>829624</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>898209</t>
+          <t>901313</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>60,92%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,16%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>232388</t>
+          <t>233759</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>284610</t>
+          <t>284227</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,25%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,95%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>214903</t>
+          <t>214353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>260693</t>
+          <t>262731</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>464141</t>
+          <t>461037</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>532447</t>
+          <t>532726</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,1%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>608594</t>
+          <t>610593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>663045</t>
+          <t>664822</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,82 +1777,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
+          <t>70,68%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>716444</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>686248</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>746316</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>69,05%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>66,14%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>71,92%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>1354169</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>1315721</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>1394510</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>68,45%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>66,51%</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
           <t>70,49%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>716444</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>685603</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>744023</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>69,05%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>66,07%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>71,7%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1353</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>1354169</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1316175</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1395635</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>68,45%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>66,53%</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>70,55%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>277627</t>
+          <t>275850</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>332078</t>
+          <t>330079</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,82 +1890,82 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>29,32%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>35,09%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>321188</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>291316</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>351384</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>30,95%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>28,08%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>33,86%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>624135</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>583794</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>662583</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>31,55%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>29,51%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>35,3%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>314</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>321188</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>293609</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>352029</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>30,95%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>28,3%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>33,93%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>636</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>624135</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>582669</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>662129</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>31,55%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>29,45%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,49%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2172811</t>
+          <t>2179290</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2281084</t>
+          <t>2280419</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2334164</t>
+          <t>2336294</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2444053</t>
+          <t>2438619</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4540249</t>
+          <t>4532346</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4681898</t>
+          <t>4684354</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,26%</t>
+          <t>68,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,43%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>992825</t>
+          <t>993490</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1101098</t>
+          <t>1094619</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>933013</t>
+          <t>938447</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1042902</t>
+          <t>1040772</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1969077</t>
+          <t>1966621</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2110726</t>
+          <t>2118629</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>31,85%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>402676</t>
+          <t>404591</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>455051</t>
+          <t>455042</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>461011</t>
+          <t>463991</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>513410</t>
+          <t>511118</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>882372</t>
+          <t>884336</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>955408</t>
+          <t>955736</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>68,66%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>242761</t>
+          <t>242770</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>295136</t>
+          <t>293221</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>180790</t>
+          <t>183082</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>233189</t>
+          <t>230209</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>436604</t>
+          <t>436276</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>509640</t>
+          <t>507676</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>635185</t>
+          <t>631273</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>694423</t>
+          <t>696741</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,0%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>720513</t>
+          <t>720867</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>778645</t>
+          <t>779546</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1373223</t>
+          <t>1374545</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1457010</t>
+          <t>1457143</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>313883</t>
+          <t>311565</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>373121</t>
+          <t>377033</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>249461</t>
+          <t>248560</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>307593</t>
+          <t>307239</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>579402</t>
+          <t>579269</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>663189</t>
+          <t>661867</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,5%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>444974</t>
+          <t>449881</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>506777</t>
+          <t>506673</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>501287</t>
+          <t>496509</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>554384</t>
+          <t>552326</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>71,65%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>964089</t>
+          <t>967649</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1043129</t>
+          <t>1041813</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>243542</t>
+          <t>243646</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>305345</t>
+          <t>300438</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>219384</t>
+          <t>221442</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>272481</t>
+          <t>277259</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>480958</t>
+          <t>482274</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>559998</t>
+          <t>556438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>654745</t>
+          <t>653425</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>711408</t>
+          <t>709600</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>794413</t>
+          <t>799826</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>848920</t>
+          <t>851864</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,23%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1469872</t>
+          <t>1467744</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1546402</t>
+          <t>1545606</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,88%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>231152</t>
+          <t>232960</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>287815</t>
+          <t>289135</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>24,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>193238</t>
+          <t>190294</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>247745</t>
+          <t>242332</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>438316</t>
+          <t>439112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>514846</t>
+          <t>516974</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,05%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2198487</t>
+          <t>2197132</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2310203</t>
+          <t>2310843</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2540611</t>
+          <t>2538399</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2644727</t>
+          <t>2645490</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4763531</t>
+          <t>4769576</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4918237</t>
+          <t>4920842</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,93%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1088794</t>
+          <t>1088154</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1200510</t>
+          <t>1201865</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>893505</t>
+          <t>892742</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>997621</t>
+          <t>999833</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2018992</t>
+          <t>2016387</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>2173698</t>
+          <t>2167653</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>503819</t>
+          <t>503349</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>547481</t>
+          <t>547892</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>534675</t>
+          <t>538437</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>575447</t>
+          <t>575579</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,81%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1056548</t>
+          <t>1054250</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1111498</t>
+          <t>1113699</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>78,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>82,95%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>125173</t>
+          <t>124762</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>168835</t>
+          <t>169305</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94507</t>
+          <t>94375</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135279</t>
+          <t>131517</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>231110</t>
+          <t>228909</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>286060</t>
+          <t>288358</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>751709</t>
+          <t>751860</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>808771</t>
+          <t>805565</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>839626</t>
+          <t>839030</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>890284</t>
+          <t>885024</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1606270</t>
+          <t>1605696</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1683892</t>
+          <t>1678775</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>209583</t>
+          <t>212789</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>266645</t>
+          <t>266494</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>149668</t>
+          <t>154928</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>200326</t>
+          <t>200922</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>374415</t>
+          <t>379532</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>452037</t>
+          <t>452611</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>606641</t>
+          <t>606843</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>647912</t>
+          <t>647827</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>628404</t>
+          <t>628716</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>670433</t>
+          <t>670175</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1245641</t>
+          <t>1248096</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1305886</t>
+          <t>1306016</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,5%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>103782</t>
+          <t>103867</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>145053</t>
+          <t>144851</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>105322</t>
+          <t>105580</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>147351</t>
+          <t>147039</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>221562</t>
+          <t>221432</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>281807</t>
+          <t>279352</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>711487</t>
+          <t>710433</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>760404</t>
+          <t>758745</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>791719</t>
+          <t>789272</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>843961</t>
+          <t>845844</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>76,42%</t>
+          <t>76,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1516486</t>
+          <t>1516819</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1589244</t>
+          <t>1590253</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>76,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,66%</t>
+          <t>80,71%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>173842</t>
+          <t>175501</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>222759</t>
+          <t>223813</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>192059</t>
+          <t>190176</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>244301</t>
+          <t>246748</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>381021</t>
+          <t>380012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>453779</t>
+          <t>453446</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>23,01%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2620694</t>
+          <t>2625373</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2717371</t>
+          <t>2718147</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2844493</t>
+          <t>2848419</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2937690</t>
+          <t>2940170</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5497943</t>
+          <t>5492814</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5625830</t>
+          <t>5627169</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,57%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>659577</t>
+          <t>658801</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>756254</t>
+          <t>751575</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>583990</t>
+          <t>581510</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>677187</t>
+          <t>673261</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1272799</t>
+          <t>1271460</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1400686</t>
+          <t>1405815</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>366201</t>
+          <t>404045</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>334289</t>
+          <t>373099</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>393082</t>
+          <t>430516</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>59,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>407975</t>
+          <t>445842</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>386820</t>
+          <t>421252</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>431261</t>
+          <t>467396</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,28%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>774177</t>
+          <t>849887</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>735417</t>
+          <t>812404</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>807426</t>
+          <t>886151</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>63,2%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>263674</t>
+          <t>280525</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>236793</t>
+          <t>254054</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>295586</t>
+          <t>311471</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>252694</t>
+          <t>271746</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>229408</t>
+          <t>250192</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>273849</t>
+          <t>296336</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>516368</t>
+          <t>552270</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>483119</t>
+          <t>516006</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>555128</t>
+          <t>589753</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,06%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>629875</t>
+          <t>684570</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>629875</t>
+          <t>684570</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>629875</t>
+          <t>684570</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>660669</t>
+          <t>717588</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>660669</t>
+          <t>717588</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>660669</t>
+          <t>717588</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1290545</t>
+          <t>1402157</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1290545</t>
+          <t>1402157</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1290545</t>
+          <t>1402157</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>598455</t>
+          <t>671284</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>309035</t>
+          <t>633116</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>766186</t>
+          <t>703672</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>50,55%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>626716</t>
+          <t>713274</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>600150</t>
+          <t>684687</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>651886</t>
+          <t>740068</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>67,38%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1225171</t>
+          <t>1384559</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>816545</t>
+          <t>1338383</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1397766</t>
+          <t>1426802</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>68,06%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>585380</t>
+          <t>366507</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>417649</t>
+          <t>334119</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>874800</t>
+          <t>404675</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>49,45%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>320910</t>
+          <t>345271</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>295740</t>
+          <t>318477</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>347476</t>
+          <t>373858</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>906291</t>
+          <t>711778</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>733696</t>
+          <t>669535</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1314917</t>
+          <t>757954</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>36,16%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1183835</t>
+          <t>1037791</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1183835</t>
+          <t>1037791</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1183835</t>
+          <t>1037791</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>947626</t>
+          <t>1058545</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>947626</t>
+          <t>1058545</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>947626</t>
+          <t>1058545</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2131462</t>
+          <t>2096337</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2131462</t>
+          <t>2096337</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2131462</t>
+          <t>2096337</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>447636</t>
+          <t>518495</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>416787</t>
+          <t>484790</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>477995</t>
+          <t>550864</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>65,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>441556</t>
+          <t>519314</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>375365</t>
+          <t>492765</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>472534</t>
+          <t>543660</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>889191</t>
+          <t>1037809</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>805862</t>
+          <t>994291</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>932733</t>
+          <t>1077091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>62,61%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>67,41%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>251024</t>
+          <t>276066</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>220665</t>
+          <t>243697</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>281873</t>
+          <t>309771</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>30,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>279937</t>
+          <t>284063</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>248959</t>
+          <t>259717</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>346128</t>
+          <t>310612</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>530961</t>
+          <t>560129</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>487419</t>
+          <t>520847</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>614290</t>
+          <t>603647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>37,78%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>698660</t>
+          <t>794561</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>698660</t>
+          <t>794561</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>698660</t>
+          <t>794561</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>721493</t>
+          <t>803377</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>721493</t>
+          <t>803377</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>721493</t>
+          <t>803377</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1420152</t>
+          <t>1597938</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1420152</t>
+          <t>1597938</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1420152</t>
+          <t>1597938</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>536323</t>
+          <t>589820</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>500287</t>
+          <t>555152</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>568636</t>
+          <t>623028</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>604981</t>
+          <t>673503</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>485438</t>
+          <t>646204</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>656680</t>
+          <t>703359</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>58,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>63,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1141304</t>
+          <t>1263324</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1010207</t>
+          <t>1218711</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1199175</t>
+          <t>1306104</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>57,23%</t>
+          <t>60,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>62,73%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>379738</t>
+          <t>389614</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>347425</t>
+          <t>356406</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>415774</t>
+          <t>424282</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>473107</t>
+          <t>429300</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>421408</t>
+          <t>399444</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>592650</t>
+          <t>456599</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>36,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,97%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>852845</t>
+          <t>818914</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>794974</t>
+          <t>776134</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>983942</t>
+          <t>863527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>42,77%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>39,87%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>41,47%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>916061</t>
+          <t>979434</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>916061</t>
+          <t>979434</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>916061</t>
+          <t>979434</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1078088</t>
+          <t>1102803</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1078088</t>
+          <t>1102803</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1078088</t>
+          <t>1102803</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1994149</t>
+          <t>2082238</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1994149</t>
+          <t>2082238</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1994149</t>
+          <t>2082238</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1948615</t>
+          <t>2183645</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1502962</t>
+          <t>2119131</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2115993</t>
+          <t>2243836</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2081228</t>
+          <t>2351934</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1933782</t>
+          <t>2299379</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2152435</t>
+          <t>2411260</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,74%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>4029843</t>
+          <t>4535579</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3540564</t>
+          <t>4453342</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4221190</t>
+          <t>4622930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>64,4%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1479816</t>
+          <t>1312712</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1312438</t>
+          <t>1252521</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1925469</t>
+          <t>1377226</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1326648</t>
+          <t>1330379</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1255441</t>
+          <t>1271053</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1474094</t>
+          <t>1382934</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2806464</t>
+          <t>2643091</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2615117</t>
+          <t>2555740</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3295743</t>
+          <t>2725328</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>35,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>37,96%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3428431</t>
+          <t>3496357</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3428431</t>
+          <t>3496357</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3428431</t>
+          <t>3496357</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3407876</t>
+          <t>3682313</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3407876</t>
+          <t>3682313</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3407876</t>
+          <t>3682313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6836307</t>
+          <t>7178670</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6836307</t>
+          <t>7178670</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6836307</t>
+          <t>7178670</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
